--- a/tests/cases_test.xlsx
+++ b/tests/cases_test.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thomas/Documents/_Plato/Plato/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8BD6594-7CF8-0C4D-BB36-94A68D3E5304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A76F59-1E50-B948-B021-008C6D9826B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16260" xr2:uid="{0A9D0FCF-1F4B-5247-B35D-CBB46409C9D9}"/>
+    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16260" activeTab="1" xr2:uid="{0A9D0FCF-1F4B-5247-B35D-CBB46409C9D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
   <si>
     <t>Name</t>
   </si>
@@ -60,6 +61,15 @@
   </si>
   <si>
     <t>sediment_thickness</t>
+  </si>
+  <si>
+    <t>ref</t>
+  </si>
+  <si>
+    <t>nnr</t>
+  </si>
+  <si>
+    <t>syn_nnr</t>
   </si>
 </sst>
 </file>
@@ -498,4 +508,57 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3288BC15-9473-3C46-93B5-57CBA9ED7537}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="20.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>